--- a/Doc/requirement/System Requirement Specification.xlsx
+++ b/Doc/requirement/System Requirement Specification.xlsx
@@ -11,7 +11,7 @@
     <sheet name="需求层次划分" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">系统需求!$A$1:$E$63</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">系统需求!$A$1:$F$163</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">需求层次划分!$A$1:$C$18</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="279">
   <si>
     <t>No</t>
   </si>
@@ -31,6 +31,9 @@
   </si>
   <si>
     <t>需求内容</t>
+  </si>
+  <si>
+    <t>方案</t>
   </si>
   <si>
     <t>关联需求和资源</t>
@@ -198,6 +201,162 @@
     <t>任务可以是定时触发的，也可以是事件触发</t>
   </si>
   <si>
+    <t>SRS_TASK_01004</t>
+  </si>
+  <si>
+    <t>TaskManager</t>
+  </si>
+  <si>
+    <t>taskManager基于APScheduler的BackgroundScheduler派生</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01005</t>
+  </si>
+  <si>
+    <t>taskManager的输入参数</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01006</t>
+  </si>
+  <si>
+    <t>TaskBase的定义</t>
+  </si>
+  <si>
+    <t>1.Task通过task_name用于唯一定义任务名
+2.与一个func对应，用于执行相应的功能
+3.拥有一个trigger，用于触发任务。该trigger用于定义APScheduler中的trigger
+4.param通过dict的方式定义，用于向func中传入参数
+5.flag用于定义该Task在任务列表中是新增还是修改</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01007</t>
+  </si>
+  <si>
+    <t>TaskBase的trigger定义</t>
+  </si>
+  <si>
+    <t>TaskBase的trigger基于CronTrigger，他有7种类型
+1. day_of_week: 输入0-6来分辨是每周的第几天运行
+2. day：输入每个月的第几天来定时运行
+3. hour：每天的特定小时运行
+4. time：每天的特定时间运行，其中hour代表小时，minite代表分钟
+5. work_day：表示只在工作日运行。其输入参数有3个。day_of_week的输入为字符串，是星期一到星期五的单词前3个字母。将这些日子通过半角逗号连接起来。根据解析到的时间格式hh:mm来输入给Crontrigger，hour代表小时，minute代表分钟。
+6. sat：与work_day类似，day_of_week为sat，其余一致。
+7. sun：与sat一致
+8. 如果是weekend，则day_of_week输入sat,sun，其余与sat保持一致。
+除了上述参数外，每类trigger都要输入timezone参数，默认是shanghai的时区</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01008</t>
+  </si>
+  <si>
+    <t>TaskBase的from_dict方法</t>
+  </si>
+  <si>
+    <t>1. TaskBase的from_dict方法是一个cls方法
+2.TaskBase的from_dict方法用于将json模型转换为一个task对象</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01009</t>
+  </si>
+  <si>
+    <t>TaskManger的定义</t>
+  </si>
+  <si>
+    <t>1.name用于定义该模块的名称
+2.timezone用于定义时区，默认为shanghai时区
+3.task_file用于从外部读取一个json配置文件</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01010</t>
+  </si>
+  <si>
+    <t>TaskManager继承</t>
+  </si>
+  <si>
+    <t>TaskManager基础自APScheduler的BackgroudScheduler类，并且通过super的方式实现init方法</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01011</t>
+  </si>
+  <si>
+    <t>TaskManager的成员</t>
+  </si>
+  <si>
+    <t>1. name用于标记名称
+2. start_time用于记录启动时间，以初始化的当前时间为准。
+3. task_list是一个列表对象，用于保存当前的任务集合</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01012</t>
+  </si>
+  <si>
+    <t>TaskManager的接口</t>
+  </si>
+  <si>
+    <t>1. load_task用于从BackgroundScheduler的持久化存储中加载任务
+2. read_task_from_file用于从json文件中读取任务，一般会将该结果与task_list做比较后进行处理。
+3. report用于从BackgroundScheduler中读取任务列表并打印出来
+4. update_task用于更新任务列表</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01013</t>
+  </si>
+  <si>
+    <t>load_task</t>
+  </si>
+  <si>
+    <t>load_task通过从BackgroudScheduler中直接读取任务列表</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01014</t>
+  </si>
+  <si>
+    <t>read_task_from_file</t>
+  </si>
+  <si>
+    <t>通过从json文件读取json对象，将每一个json对象转换为一个taskBase对象，并加入到TaskManger的task_list中。</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01015</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
+    <t>1. 返回任务管理器中有多少任务，报告出来
+2. 根据taskmanager中的start_time计算manager运行了多少时间，以多少小时多少分钟的方式来表达。有可能服务器已经运行了超过24小时，要把时间转换为纯粹的小时数。</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01016</t>
+  </si>
+  <si>
+    <t>update_task</t>
+  </si>
+  <si>
+    <t>通过load_task获得当前任务列表
+通过read_task_from_file获得配置文件中的任务列表
+对比上面两个任务列表，如过配置文件的任务列表中的任务与当前任务列表中的任务名称和其它信息全一致，则标记为U，表示未更新。如果名称一致，其它信息不一致，则标记为M，表示修改。如果找不到名称，则标记为A，表示新增。</t>
+  </si>
+  <si>
+    <t>SRS_TASK_01017</t>
+  </si>
+  <si>
+    <t>task_file的数据定义</t>
+  </si>
+  <si>
+    <t>1. task_file是一个json文件
+2. 它其中每一个json对象定义了一个任务，通过以下键值对来表达
+3. task_name表示任务名称
+4. trigger通过不同类型的关键字来代表不同的任务调度方式。
+4.1  day_of_week: 0~6 stands for sun to sat.
+4.2  day        : 1~31 stands for day in month.
+4.3  hour       : 18 stands for 18:00.
+4.4  time       : 18:31 stands for real time.
+4.5  work day   : in time format like 18:31, means time on work day.
+4.6  sat, sun   : the same like work day</t>
+  </si>
+  <si>
     <t>SRS_AI_01001</t>
   </si>
   <si>
@@ -205,9 +364,6 @@
   </si>
   <si>
     <t>AI业务分为数据处理、模型训练、模型验证、模型持久化和模型运行</t>
-  </si>
-  <si>
-    <t>SRS_TASK_01004</t>
   </si>
   <si>
     <t>任务调度需求</t>
@@ -360,6 +516,374 @@
   </si>
   <si>
     <t>应用无监督学习法构造分类，应用1d CNN网络进行学习，对日K线进行筛选，选择合适的形态作为短期标的池。</t>
+  </si>
+  <si>
+    <t>SRS_DATA_</t>
+  </si>
+  <si>
+    <t>数据采集和清洗模块</t>
+  </si>
+  <si>
+    <t>支持从多个数据源获取股票行情数据、财务数据、新闻等信息。</t>
+  </si>
+  <si>
+    <t>URL管理器</t>
+  </si>
+  <si>
+    <t>该模块负责管理待抓取的 URL 集合，以确保系统能够全面覆盖目标站点并避免重复抓取。可以使用队列、哈希表等数据结构来实现 URL 管理器，并根据优先级和更新时间等因素进行 URL 调度和排序。</t>
+  </si>
+  <si>
+    <t>URL管理器的定义</t>
+  </si>
+  <si>
+    <t>URL管理器的持久化</t>
+  </si>
+  <si>
+    <t>URL管理器基于SQLite数据库实现持久化</t>
+  </si>
+  <si>
+    <t>URL管理器的初始化</t>
+  </si>
+  <si>
+    <t>URL管理器的初始化直接读取从数据中心给出的数据</t>
+  </si>
+  <si>
+    <t>URL管理器的管理</t>
+  </si>
+  <si>
+    <t>URL管理器均以操作自己的url_list来实现管理</t>
+  </si>
+  <si>
+    <t>URL对象的定义</t>
+  </si>
+  <si>
+    <t>URL对象以dict格式定义，包含以下内容
+1. url：记录url地址
+2. parser：用于解析的解析器函数
+3. download：用于下载的下载器函数
+4. status：url的状态，用于记录是否已经爬取
+status为0，则表示待下载，status为200则表示已经下载，status为4x或5x则表示下载失败</t>
+  </si>
+  <si>
+    <t>URL的存储</t>
+  </si>
+  <si>
+    <t>URL管理器将当前url_list中的url对象全部存储到数据库，并清空url_list</t>
+  </si>
+  <si>
+    <t>未爬取URL的管理</t>
+  </si>
+  <si>
+    <t>从数据库中读取未爬取的URL，一次以1000为默认值</t>
+  </si>
+  <si>
+    <t>实现 URL 添加方法</t>
+  </si>
+  <si>
+    <t>URL 管理器需要提供添加 URL 的方法，以便将待爬取的 URL 加入到 URL 集合中。add_new_url(url) 方法来实现URL的添加，并对重复URL进行去重处理。</t>
+  </si>
+  <si>
+    <t>实现 URL 获取方法</t>
+  </si>
+  <si>
+    <t>URL管理器通过get_url方法给出一个URL对象，并从自身的url_list当中去掉该对象。</t>
+  </si>
+  <si>
+    <t>实现 URL 记录方法</t>
+  </si>
+  <si>
+    <t>当爬取完成后，下载器会返回一个URL对象给URL管理器，URL管理器将其加入自己的url_list当中</t>
+  </si>
+  <si>
+    <t>实现 URL 集合管理方法</t>
+  </si>
+  <si>
+    <t>统计url_list当中的url对象的status，并反馈输出的url数量，成功的url数量</t>
+  </si>
+  <si>
+    <t>Header管理器</t>
+  </si>
+  <si>
+    <t>Header管理器从SQLite数据库中读取http header，然后以固定的方式或随机的方式返回header</t>
+  </si>
+  <si>
+    <t>每个订阅者以特定id的方式发请求，header管理器根据id所对应的策略来返回header</t>
+  </si>
+  <si>
+    <t>Header管理器订阅</t>
+  </si>
+  <si>
+    <t>每个需求者发送一个请求给header管理器，header管理器会返回一个订阅码</t>
+  </si>
+  <si>
+    <t>Header管理器续约</t>
+  </si>
+  <si>
+    <t>每隔一段时间，需求者发送续约请求给header管理器，header管理器把对应的id其合约时间延时。如果超时则退订</t>
+  </si>
+  <si>
+    <t>下载器</t>
+  </si>
+  <si>
+    <t>网页下载器：该模块负责下载指定 URL 的网页内容，并将结果返回给解析器进行后续处理。可以使用requests 来实现网页下载器，并支持多线程、代理、Cookie 等功能。</t>
+  </si>
+  <si>
+    <t>下载器的下载功能</t>
+  </si>
+  <si>
+    <t>下载器返回3类数据
+1、URL对象，即修改过status的URL对象
+2、url_list, 直接解析的urls用于下一步解析
+3、data，直接下载的数据</t>
+  </si>
+  <si>
+    <t>多线程下载</t>
+  </si>
+  <si>
+    <t>地址过滤器</t>
+  </si>
+  <si>
+    <t>能够提取所有的地址的过滤器</t>
+  </si>
+  <si>
+    <t>地址处理器</t>
+  </si>
+  <si>
+    <t>对url增加prefix</t>
+  </si>
+  <si>
+    <t>过滤特定的url</t>
+  </si>
+  <si>
+    <t>csv2df</t>
+  </si>
+  <si>
+    <t>将CSV转换为DataFrame</t>
+  </si>
+  <si>
+    <t>data2db</t>
+  </si>
+  <si>
+    <t>将DataFrame存入mysql</t>
+  </si>
+  <si>
+    <t>内容解析器：该模块负责解析网页内容，提取所需的数据，并将结果存储到数据库或文件系统中。可以使用正则表达式、BeautifulSoup、XPath 等技术来实现内容解析器，并考虑数据结构和类型转换等问题。</t>
+  </si>
+  <si>
+    <t>数据存储器：该模块负责将解析得到的数据存储到数据库、文件系统或其他存储介质中。可以使用关系型数据库、非关系型数据库、HDFS 等技术来实现数据存储器，并考虑数据去重、更新和查询等问题。</t>
+  </si>
+  <si>
+    <t>日志记录器：该模块负责记录爬虫系统的运行状态和异常信息，以便后续分析和处理。可以使用 log4j、logging 等库来实现日志记录器，并考虑日志级别、格式、滚动等问题。</t>
+  </si>
+  <si>
+    <t>配置管理器：该模块负责管理爬虫系统的配置文件，包括 URL 列表、下载器参数、解析器规则、存储器类型等内容。可以使用 YAML、JSON、XML 等格式来实现配置管理器，并支持动态修改和加载。</t>
+  </si>
+  <si>
+    <t>分布式控制器：该模块负责对多个爬虫节点进行协调和控制，以实现分布式爬取和数据合并。可以使用 ZooKeeper、Redis 等分布式协作框架来实现控制器，并考虑任务分配、节点故障等情况。</t>
+  </si>
+  <si>
+    <t>能够定期自动抓取数据，并支持手动触发采集。</t>
+  </si>
+  <si>
+    <t>支持缓存数据，避免重复下载和处理。</t>
+  </si>
+  <si>
+    <t>能够清洗和转换数据格式，使其符合分析和建模的要求。</t>
+  </si>
+  <si>
+    <t>数据分析和建模模块</t>
+  </si>
+  <si>
+    <t>支持基础的统计学分析功能，如平均值、标准差、相关系数等。</t>
+  </si>
+  <si>
+    <t>能够使用机器学习、深度学习、时间序列分析等技术来进行分析和建模。</t>
+  </si>
+  <si>
+    <t>支持多种算法和技术，如回归、分类、聚类、神经网络等。</t>
+  </si>
+  <si>
+    <t>能够自动调整参数、优化算法，并提供结果可视化和报告输出。</t>
+  </si>
+  <si>
+    <t>用户界面和交互模块</t>
+  </si>
+  <si>
+    <t>提供友好的用户界面和操作体验，支持多设备访问（电脑、手机）。</t>
+  </si>
+  <si>
+    <t>能够快速查询股票行情、公司财务数据、新闻资讯等信息。</t>
+  </si>
+  <si>
+    <t>提供股票池筛选、趋势预测、组合配置等功能。</t>
+  </si>
+  <si>
+    <t>支持自定义查询和报告，以及数据导出和分享。</t>
+  </si>
+  <si>
+    <t>组合管理和风控模块</t>
+  </si>
+  <si>
+    <t>能够实现资产配置、标的选择、交易执行等功能。</t>
+  </si>
+  <si>
+    <t>支持多因子模型、动态风险控制等技术来进行组合管理和风险控制。</t>
+  </si>
+  <si>
+    <t>能够计算投资回报率、最大回撤、夏普比率等指标，并提供策略回测和优化工具。</t>
+  </si>
+  <si>
+    <t>支持设置止损、止盈、仓位控制等风控规则，避免过度风险和损失。</t>
+  </si>
+  <si>
+    <t>实时监控和报警模块</t>
+  </si>
+  <si>
+    <t>能够实时监控市场动态、用户组合的变化等情况。</t>
+  </si>
+  <si>
+    <t>支持推送通知、短信、邮件等多种方式进行报警。</t>
+  </si>
+  <si>
+    <t>针对不同类型的事件，提供不同级别的报警和处理方法。</t>
+  </si>
+  <si>
+    <t>能够生成日志记录、错误诊断和信息反馈，便于后续分析和处理。</t>
+  </si>
+  <si>
+    <t>系统部署和运维模块</t>
+  </si>
+  <si>
+    <t>能够支持系统快速部署、容器化等技术。</t>
+  </si>
+  <si>
+    <t>提供日志记录、错误诊断和故障恢复等工具和方法。</t>
+  </si>
+  <si>
+    <t>能够进行性能测试和负载均衡，保证系统的稳定性和可靠性。</t>
+  </si>
+  <si>
+    <t>支持扩展和升级，以适应不断变化的需求和环境。</t>
+  </si>
+  <si>
+    <t>数据来源</t>
+  </si>
+  <si>
+    <t>证券市场数据</t>
+  </si>
+  <si>
+    <t>经济数据</t>
+  </si>
+  <si>
+    <t>外部数据源-天气</t>
+  </si>
+  <si>
+    <t>新闻数据</t>
+  </si>
+  <si>
+    <t>数据清洗</t>
+  </si>
+  <si>
+    <t>数据存储</t>
+  </si>
+  <si>
+    <t>数据分析</t>
+  </si>
+  <si>
+    <t>策略制定</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：根据数据分析结果制定交易策略</t>
+    </r>
+  </si>
+  <si>
+    <t>风险控制</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：控制交易风险，避免过度投资或亏损</t>
+    </r>
+  </si>
+  <si>
+    <t>交易执行</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：根据制定的交易策略，自动执行交易指令</t>
+    </r>
+  </si>
+  <si>
+    <t>统计报表</t>
+  </si>
+  <si>
+    <t>对交易数据进行统计分析，输出报表</t>
+  </si>
+  <si>
+    <t>实时监控</t>
+  </si>
+  <si>
+    <t>对交易情况进行实时监控，提醒用户关注异常情况</t>
+  </si>
+  <si>
+    <t>数据中心的接口方案</t>
+  </si>
+  <si>
+    <t>采用Django REST framework来实现RESTful API</t>
   </si>
   <si>
     <t>需求级别</t>
@@ -462,7 +986,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +998,41 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF6796E6"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -619,6 +1178,18 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -956,10 +1527,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -968,137 +1539,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1120,13 +1691,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1477,711 +2078,1961 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
+  <dimension ref="A1:F182"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.55555555555556" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.4444444444444" style="2" customWidth="1"/>
-    <col min="3" max="3" width="32.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="58.7777777777778" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.6666666666667" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="2" max="2" width="16.4444444444444" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.5555555555556" style="3" customWidth="1"/>
+    <col min="5" max="5" width="46.5555555555556" style="3" customWidth="1"/>
+    <col min="6" max="6" width="24.6666666666667" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" ht="124.8" spans="1:5">
-      <c r="A2" s="5">
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="92.4" spans="1:6">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="12"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" ht="66" spans="1:6">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="26.4" spans="1:6">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" ht="39.6" spans="1:6">
+      <c r="A8" s="8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="8">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="11" ht="39.6" spans="1:6">
+      <c r="A11" s="8">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="B11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="8">
         <v>7</v>
       </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" ht="78" spans="1:5">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" ht="26.4" spans="1:6">
+      <c r="A22" s="8">
         <v>8</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B22" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="8">
         <v>9</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="B23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="8">
         <v>10</v>
       </c>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6" t="s">
+      <c r="B24" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" ht="26.4" spans="1:6">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" ht="14.4" spans="1:6">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" ht="79.2" spans="1:6">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" ht="237.6" spans="1:6">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" ht="39.6" spans="1:6">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" ht="39.6" spans="1:6">
+      <c r="A30" s="8"/>
+      <c r="B30" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="11"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" ht="39.6" spans="1:6">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="11"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" ht="52.8" spans="1:6">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="11"/>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" ht="92.4" spans="1:6">
+      <c r="A33" s="8"/>
+      <c r="B33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" ht="26.4" spans="1:6">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="11"/>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" ht="39.6" spans="1:6">
+      <c r="A35" s="8"/>
+      <c r="B35" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="11"/>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" ht="66" spans="1:6">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="11"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" ht="92.4" spans="1:6">
+      <c r="A37" s="8"/>
+      <c r="B37" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="11"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" ht="171.6" spans="1:6">
+      <c r="A38" s="8"/>
+      <c r="B38" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="11"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" ht="14.4" spans="1:6">
+      <c r="A39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" ht="14.4" spans="1:6">
+      <c r="A40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" ht="14.4" spans="1:6">
+      <c r="A41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" ht="14.4" spans="1:6">
+      <c r="A42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" ht="14.4" spans="1:6">
+      <c r="A43" s="8"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" ht="14.4" spans="1:6">
+      <c r="A44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" ht="14.4" spans="1:6">
+      <c r="A45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="12"/>
+    </row>
+    <row r="46" ht="26.4" spans="1:6">
+      <c r="A46" s="8">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B46" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E46" s="11"/>
+      <c r="F46" s="12"/>
+    </row>
+    <row r="47" ht="26.4" spans="1:6">
+      <c r="A47" s="8">
         <v>12</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8" t="s">
+      <c r="B47" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" s="11"/>
+      <c r="F47" s="12"/>
+    </row>
+    <row r="48" ht="26.4" spans="1:6">
+      <c r="A48" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" ht="31.2" spans="1:5">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6" t="s">
+      <c r="B48" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" s="11"/>
+      <c r="F48" s="12"/>
+    </row>
+    <row r="49" ht="39.6" spans="1:6">
+      <c r="A49" s="8">
         <v>14</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B49" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E49" s="11"/>
+      <c r="F49" s="12"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="8">
         <v>15</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="B50" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E50" s="11"/>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="8"/>
+      <c r="B51" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" s="11"/>
+      <c r="F51" s="12"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="8"/>
+      <c r="B52" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" s="11"/>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="8"/>
+      <c r="B53" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E53" s="11"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="8"/>
+      <c r="B54" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" s="11"/>
+      <c r="F54" s="12"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="8">
         <v>16</v>
       </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" ht="31.2" spans="1:5">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6" t="s">
+      <c r="B55" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E55" s="11"/>
+      <c r="F55" s="12"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="8"/>
+      <c r="B56" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" s="11"/>
+      <c r="F56" s="12"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="8"/>
+      <c r="B57" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E57" s="11"/>
+      <c r="F57" s="12"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="8"/>
+      <c r="B58" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E58" s="11"/>
+      <c r="F58" s="12"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="8"/>
+      <c r="B59" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="12"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="8"/>
+      <c r="B60" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="8"/>
+      <c r="B61" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="10"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="12"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="8"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="12"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="8"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="12"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="8">
         <v>17</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="12"/>
+    </row>
+    <row r="65" ht="26.4" spans="1:6">
+      <c r="A65" s="8"/>
+      <c r="B65" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E65" s="11"/>
+      <c r="F65" s="12"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="8"/>
+      <c r="B66" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E66" s="11"/>
+      <c r="F66" s="12"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="8"/>
+      <c r="B67" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E67" s="11"/>
+      <c r="F67" s="12"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="8"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="12"/>
+    </row>
+    <row r="69" ht="26.4" spans="1:6">
+      <c r="A69" s="8"/>
+      <c r="B69" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E69" s="11"/>
+      <c r="F69" s="12"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="8"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="12"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="8"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="12"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="8"/>
+      <c r="B72" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E72" s="11"/>
+      <c r="F72" s="12"/>
+    </row>
+    <row r="73" ht="14.4" spans="1:6">
+      <c r="A73" s="8"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E73" s="11"/>
+      <c r="F73" s="12"/>
+    </row>
+    <row r="74" ht="52.8" spans="1:6">
+      <c r="A74" s="8"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E74" s="15"/>
+      <c r="F74" s="12"/>
+    </row>
+    <row r="75" ht="14.4" spans="1:6">
+      <c r="A75" s="8"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="12"/>
+    </row>
+    <row r="76" ht="14.4" spans="1:6">
+      <c r="A76" s="8"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E76" s="15"/>
+      <c r="F76" s="12"/>
+    </row>
+    <row r="77" ht="14.4" spans="1:6">
+      <c r="A77" s="8"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="E77" s="15"/>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="78" ht="14.4" spans="1:6">
+      <c r="A78" s="8"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E78" s="15"/>
+      <c r="F78" s="12"/>
+    </row>
+    <row r="79" ht="92.4" spans="1:6">
+      <c r="A79" s="8"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="E79" s="15"/>
+      <c r="F79" s="12"/>
+    </row>
+    <row r="80" ht="26.4" spans="1:6">
+      <c r="A80" s="8"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="E80" s="15"/>
+      <c r="F80" s="12"/>
+    </row>
+    <row r="81" ht="14.4" spans="1:6">
+      <c r="A81" s="8"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="E81" s="15"/>
+      <c r="F81" s="12"/>
+    </row>
+    <row r="82" ht="39.6" spans="1:6">
+      <c r="A82" s="8"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="E82" s="15"/>
+      <c r="F82" s="12"/>
+    </row>
+    <row r="83" ht="26.4" spans="1:6">
+      <c r="A83" s="8"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="E83" s="15"/>
+      <c r="F83" s="12"/>
+    </row>
+    <row r="84" ht="26.4" spans="1:6">
+      <c r="A84" s="8"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E84" s="15"/>
+      <c r="F84" s="12"/>
+    </row>
+    <row r="85" ht="26.4" spans="1:6">
+      <c r="A85" s="8"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="E85" s="15"/>
+      <c r="F85" s="12"/>
+    </row>
+    <row r="86" ht="26.4" spans="1:6">
+      <c r="A86" s="8"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="E86" s="15"/>
+      <c r="F86" s="12"/>
+    </row>
+    <row r="87" ht="26.4" spans="1:6">
+      <c r="A87" s="8"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E87" s="15"/>
+      <c r="F87" s="12"/>
+    </row>
+    <row r="88" ht="26.4" spans="1:6">
+      <c r="A88" s="8"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="E88" s="15"/>
+      <c r="F88" s="12"/>
+    </row>
+    <row r="89" ht="39.6" spans="1:6">
+      <c r="A89" s="8"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E89" s="15"/>
+      <c r="F89" s="12"/>
+    </row>
+    <row r="90" ht="39.6" spans="1:6">
+      <c r="A90" s="8"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E90" s="15"/>
+      <c r="F90" s="12"/>
+    </row>
+    <row r="91" ht="52.8" spans="1:6">
+      <c r="A91" s="8"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E91" s="15"/>
+      <c r="F91" s="12"/>
+    </row>
+    <row r="92" ht="14.4" spans="1:6">
+      <c r="A92" s="8"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D92" s="10"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="12"/>
+    </row>
+    <row r="93" ht="14.4" spans="1:6">
+      <c r="A93" s="8"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E93" s="15"/>
+      <c r="F93" s="12"/>
+    </row>
+    <row r="94" ht="14.4" spans="1:6">
+      <c r="A94" s="8"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="E94" s="15"/>
+      <c r="F94" s="12"/>
+    </row>
+    <row r="95" ht="14.4" spans="1:6">
+      <c r="A95" s="8"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E95" s="15"/>
+      <c r="F95" s="12"/>
+    </row>
+    <row r="96" ht="14.4" spans="1:6">
+      <c r="A96" s="8"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E96" s="15"/>
+      <c r="F96" s="12"/>
+    </row>
+    <row r="97" ht="14.4" spans="1:6">
+      <c r="A97" s="8"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="E97" s="15"/>
+      <c r="F97" s="12"/>
+    </row>
+    <row r="98" ht="14.4" spans="1:6">
+      <c r="A98" s="8"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="12"/>
+    </row>
+    <row r="99" ht="52.8" spans="1:6">
+      <c r="A99" s="8"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="E99" s="15"/>
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" ht="52.8" spans="1:6">
+      <c r="A100" s="8"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E100" s="15"/>
+      <c r="F100" s="12"/>
+    </row>
+    <row r="101" ht="39.6" spans="1:6">
+      <c r="A101" s="8"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="10"/>
+      <c r="D101" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="E101" s="15"/>
+      <c r="F101" s="12"/>
+    </row>
+    <row r="102" ht="26.4" spans="1:6">
+      <c r="A102" s="8"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="10"/>
+      <c r="D102" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="E102" s="15"/>
+      <c r="F102" s="12"/>
+    </row>
+    <row r="103" ht="52.8" spans="1:6">
+      <c r="A103" s="8"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="10"/>
+      <c r="D103" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E103" s="15"/>
+      <c r="F103" s="12"/>
+    </row>
+    <row r="104" ht="52.8" spans="1:6">
+      <c r="A104" s="8"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E104" s="11"/>
+      <c r="F104" s="12"/>
+    </row>
+    <row r="105" ht="14.4" spans="1:6">
+      <c r="A105" s="8"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="10"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="12"/>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="8"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="10"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="12"/>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="8"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="10"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="12"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="8"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="10"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="12"/>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="8"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="10"/>
+      <c r="D109" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E109" s="11"/>
+      <c r="F109" s="12"/>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="8"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="10"/>
+      <c r="D110" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E110" s="11"/>
+      <c r="F110" s="12"/>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="8"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="10"/>
+      <c r="D111" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E111" s="11"/>
+      <c r="F111" s="12"/>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="8"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E112" s="11"/>
+      <c r="F112" s="12"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="8"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="10"/>
+      <c r="D113" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E113" s="11"/>
+      <c r="F113" s="12"/>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="8"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="10"/>
+      <c r="D114" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E114" s="11"/>
+      <c r="F114" s="12"/>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="8"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E115" s="11"/>
+      <c r="F115" s="12"/>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="8"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="10"/>
+      <c r="D116" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E116" s="11"/>
+      <c r="F116" s="12"/>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="8"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E117" s="11"/>
+      <c r="F117" s="12"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="8"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="10"/>
+      <c r="D118" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E118" s="11"/>
+      <c r="F118" s="12"/>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="8"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="10"/>
+      <c r="D119" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E119" s="11"/>
+      <c r="F119" s="12"/>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="8"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="10"/>
+      <c r="D120" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E120" s="11"/>
+      <c r="F120" s="12"/>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="8"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="10"/>
+      <c r="D121" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E121" s="11"/>
+      <c r="F121" s="12"/>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="8"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E122" s="11"/>
+      <c r="F122" s="12"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="8"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="10"/>
+      <c r="D123" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E123" s="11"/>
+      <c r="F123" s="12"/>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="8"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="10"/>
+      <c r="D124" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E124" s="11"/>
+      <c r="F124" s="12"/>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="8"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="10"/>
+      <c r="D125" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E125" s="11"/>
+      <c r="F125" s="12"/>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="8"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="10"/>
+      <c r="D126" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E126" s="11"/>
+      <c r="F126" s="12"/>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" s="8"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E127" s="11"/>
+      <c r="F127" s="12"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" s="8"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="10"/>
+      <c r="D128" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E128" s="11"/>
+      <c r="F128" s="12"/>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" s="8"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="10"/>
+      <c r="D129" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E129" s="11"/>
+      <c r="F129" s="12"/>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" s="8"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="10"/>
+      <c r="D130" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E130" s="11"/>
+      <c r="F130" s="12"/>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" s="8"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="10"/>
+      <c r="D131" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E131" s="11"/>
+      <c r="F131" s="12"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" s="8"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E132" s="11"/>
+      <c r="F132" s="12"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" s="8"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="10"/>
+      <c r="D133" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E133" s="11"/>
+      <c r="F133" s="12"/>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="8"/>
+      <c r="B134" s="9"/>
+      <c r="C134" s="10"/>
+      <c r="D134" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E134" s="11"/>
+      <c r="F134" s="12"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="8"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="10"/>
+      <c r="D135" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E135" s="11"/>
+      <c r="F135" s="12"/>
+    </row>
+    <row r="136" ht="14.4" spans="1:6">
+      <c r="A136" s="8"/>
+      <c r="B136" s="9"/>
+      <c r="C136" s="10"/>
+      <c r="D136" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E136" s="11"/>
+      <c r="F136" s="12"/>
+    </row>
+    <row r="137" ht="14.4" spans="1:6">
+      <c r="A137" s="8"/>
+      <c r="B137" s="9"/>
+      <c r="C137" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E137" s="11"/>
+      <c r="F137" s="12"/>
+    </row>
+    <row r="138" ht="14.4" spans="1:6">
+      <c r="A138" s="8"/>
+      <c r="B138" s="9"/>
+      <c r="C138" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E138" s="11"/>
+      <c r="F138" s="12"/>
+    </row>
+    <row r="139" ht="14.4" spans="1:6">
+      <c r="A139" s="8"/>
+      <c r="B139" s="9"/>
+      <c r="C139" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E139" s="11"/>
+      <c r="F139" s="12"/>
+    </row>
+    <row r="140" ht="14.4" spans="1:6">
+      <c r="A140" s="8"/>
+      <c r="B140" s="9"/>
+      <c r="C140" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E140" s="11"/>
+      <c r="F140" s="12"/>
+    </row>
+    <row r="141" ht="14.4" spans="1:6">
+      <c r="A141" s="8"/>
+      <c r="B141" s="9"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
+      <c r="F141" s="12"/>
+    </row>
+    <row r="142" ht="14.4" spans="1:6">
+      <c r="A142" s="8"/>
+      <c r="B142" s="9"/>
+      <c r="C142" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D142" s="16"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="12"/>
+    </row>
+    <row r="143" ht="14.4" spans="1:6">
+      <c r="A143" s="8"/>
+      <c r="B143" s="9"/>
+      <c r="C143" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D143" s="16"/>
+      <c r="E143" s="11"/>
+      <c r="F143" s="12"/>
+    </row>
+    <row r="144" ht="14.4" spans="1:6">
+      <c r="A144" s="8"/>
+      <c r="B144" s="9"/>
+      <c r="C144" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D144" s="16"/>
+      <c r="E144" s="11"/>
+      <c r="F144" s="12"/>
+    </row>
+    <row r="145" ht="14.4" spans="1:6">
+      <c r="A145" s="8"/>
+      <c r="B145" s="9"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="17"/>
+      <c r="E145" s="11"/>
+      <c r="F145" s="12"/>
+    </row>
+    <row r="146" ht="14.4" spans="1:6">
+      <c r="A146" s="8"/>
+      <c r="B146" s="9"/>
+      <c r="C146" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D146" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="E146" s="11"/>
+      <c r="F146" s="12"/>
+    </row>
+    <row r="147" ht="14.4" spans="1:6">
+      <c r="A147" s="8"/>
+      <c r="B147" s="9"/>
+      <c r="C147" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D147" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="E147" s="11"/>
+      <c r="F147" s="12"/>
+    </row>
+    <row r="148" ht="14.4" spans="1:6">
+      <c r="A148" s="8"/>
+      <c r="B148" s="9"/>
+      <c r="C148" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D148" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="E148" s="11"/>
+      <c r="F148" s="12"/>
+    </row>
+    <row r="149" ht="14.4" spans="1:6">
+      <c r="A149" s="8"/>
+      <c r="B149" s="9"/>
+      <c r="C149" s="11"/>
+      <c r="D149" s="11"/>
+      <c r="E149" s="11"/>
+      <c r="F149" s="12"/>
+    </row>
+    <row r="150" ht="14.4" spans="1:6">
+      <c r="A150" s="8"/>
+      <c r="B150" s="9"/>
+      <c r="C150" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="E150" s="11"/>
+      <c r="F150" s="12"/>
+    </row>
+    <row r="151" ht="14.4" spans="1:6">
+      <c r="A151" s="8"/>
+      <c r="B151" s="9"/>
+      <c r="C151" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E151" s="11"/>
+      <c r="F151" s="12"/>
+    </row>
+    <row r="152" ht="14.4" spans="1:6">
+      <c r="A152" s="8"/>
+      <c r="B152" s="9"/>
+      <c r="C152" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E152" s="11"/>
+      <c r="F152" s="12"/>
+    </row>
+    <row r="153" ht="14.4" spans="1:6">
+      <c r="A153" s="8"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="11"/>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11"/>
+      <c r="F153" s="12"/>
+    </row>
+    <row r="154" ht="14.4" spans="1:6">
+      <c r="A154" s="8"/>
+      <c r="B154" s="9"/>
+      <c r="C154" s="11"/>
+      <c r="D154" s="11"/>
+      <c r="E154" s="11"/>
+      <c r="F154" s="12"/>
+    </row>
+    <row r="155" ht="14.4" spans="1:6">
+      <c r="A155" s="8"/>
+      <c r="B155" s="9"/>
+      <c r="C155" s="11"/>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
+      <c r="F155" s="12"/>
+    </row>
+    <row r="156" ht="14.4" spans="1:6">
+      <c r="A156" s="8"/>
+      <c r="B156" s="9"/>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="12"/>
+    </row>
+    <row r="157" ht="14.4" spans="1:6">
+      <c r="A157" s="8"/>
+      <c r="B157" s="9"/>
+      <c r="C157" s="11"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="12"/>
+    </row>
+    <row r="158" ht="14.4" spans="1:6">
+      <c r="A158" s="8"/>
+      <c r="B158" s="9"/>
+      <c r="C158" s="11"/>
+      <c r="D158" s="11"/>
+      <c r="E158" s="11"/>
+      <c r="F158" s="12"/>
+    </row>
+    <row r="159" ht="14.4" spans="1:6">
+      <c r="A159" s="8"/>
+      <c r="B159" s="9"/>
+      <c r="C159" s="11"/>
+      <c r="D159" s="11"/>
+      <c r="E159" s="11"/>
+      <c r="F159" s="12"/>
+    </row>
+    <row r="160" ht="14.4" spans="1:6">
+      <c r="A160" s="8"/>
+      <c r="B160" s="9"/>
+      <c r="C160" s="11"/>
+      <c r="D160" s="11"/>
+      <c r="E160" s="11"/>
+      <c r="F160" s="12"/>
+    </row>
+    <row r="161" ht="14.4" spans="1:6">
+      <c r="A161" s="8"/>
+      <c r="B161" s="9"/>
+      <c r="C161" s="11"/>
+      <c r="D161" s="11"/>
+      <c r="E161" s="11"/>
+      <c r="F161" s="12"/>
+    </row>
+    <row r="162" ht="14.4" spans="1:6">
+      <c r="A162" s="8"/>
+      <c r="B162" s="9"/>
+      <c r="C162" s="11"/>
+      <c r="D162" s="11"/>
+      <c r="E162" s="11"/>
+      <c r="F162" s="12"/>
+    </row>
+    <row r="163" ht="14.4" spans="1:6">
+      <c r="A163" s="8">
         <v>18</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" ht="78" spans="1:5">
-      <c r="A8" s="5">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="5">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" ht="46.8" spans="1:5">
-      <c r="A11" s="5">
-        <v>6</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="8"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5">
-        <v>7</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-    </row>
-    <row r="22" ht="31.2" spans="1:5">
-      <c r="A22" s="5">
-        <v>8</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="8"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5">
-        <v>9</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="8"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5">
-        <v>10</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" ht="31.2" spans="1:5">
-      <c r="A25" s="5">
-        <v>11</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="8"/>
-    </row>
-    <row r="26" ht="31.2" spans="1:5">
-      <c r="A26" s="5">
-        <v>12</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="8"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5">
-        <v>13</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="8"/>
-    </row>
-    <row r="28" ht="46.8" spans="1:5">
-      <c r="A28" s="5">
-        <v>14</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" s="8"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5">
-        <v>15</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="8"/>
-    </row>
-    <row r="30" ht="31.2" spans="1:5">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="8"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="8"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E33" s="8"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5">
-        <v>16</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" s="8"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="8"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E36" s="8"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E37" s="8"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="8"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="8"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="8"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="8"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5">
-        <v>17</v>
-      </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="8"/>
-    </row>
-    <row r="44" ht="46.8" spans="1:5">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E44" s="8"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" s="8"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5"/>
-      <c r="B46" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" s="8"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="8"/>
-    </row>
-    <row r="48" ht="31.2" spans="1:5">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E48" s="8"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="8"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="8"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="8"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="8"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="8"/>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="8"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="8"/>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="8"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="8"/>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="8"/>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="8"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="8"/>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="8"/>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="8"/>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5">
-        <v>18</v>
-      </c>
-      <c r="B63" s="6"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="8"/>
+      <c r="B163" s="9"/>
+      <c r="C163" s="11"/>
+      <c r="D163" s="11"/>
+      <c r="E163" s="11"/>
+      <c r="F163" s="12"/>
+    </row>
+    <row r="164" ht="14.4" spans="4:5">
+      <c r="D164" s="19"/>
+      <c r="E164" s="19"/>
+    </row>
+    <row r="165" spans="4:5">
+      <c r="D165" s="19"/>
+      <c r="E165" s="19"/>
+    </row>
+    <row r="166" spans="4:5">
+      <c r="D166" s="19"/>
+      <c r="E166" s="19"/>
+    </row>
+    <row r="167" spans="4:5">
+      <c r="D167" s="19"/>
+      <c r="E167" s="19"/>
+    </row>
+    <row r="168" spans="4:5">
+      <c r="D168" s="19"/>
+      <c r="E168" s="19"/>
+    </row>
+    <row r="169" spans="4:5">
+      <c r="D169" s="19"/>
+      <c r="E169" s="19"/>
+    </row>
+    <row r="170" spans="4:5">
+      <c r="D170" s="19"/>
+      <c r="E170" s="19"/>
+    </row>
+    <row r="171" spans="4:5">
+      <c r="D171" s="19"/>
+      <c r="E171" s="19"/>
+    </row>
+    <row r="172" spans="4:5">
+      <c r="D172" s="19"/>
+      <c r="E172" s="19"/>
+    </row>
+    <row r="173" spans="4:5">
+      <c r="D173" s="19"/>
+      <c r="E173" s="19"/>
+    </row>
+    <row r="174" spans="4:5">
+      <c r="D174" s="19"/>
+      <c r="E174" s="19"/>
+    </row>
+    <row r="175" spans="4:5">
+      <c r="D175" s="19"/>
+      <c r="E175" s="19"/>
+    </row>
+    <row r="176" spans="4:5">
+      <c r="D176" s="19"/>
+      <c r="E176" s="19"/>
+    </row>
+    <row r="177" spans="4:5">
+      <c r="D177" s="19"/>
+      <c r="E177" s="19"/>
+    </row>
+    <row r="178" spans="4:5">
+      <c r="D178" s="19"/>
+      <c r="E178" s="19"/>
+    </row>
+    <row r="179" spans="4:5">
+      <c r="D179" s="19"/>
+      <c r="E179" s="19"/>
+    </row>
+    <row r="180" spans="4:5">
+      <c r="D180" s="19"/>
+      <c r="E180" s="19"/>
+    </row>
+    <row r="181" spans="4:5">
+      <c r="D181" s="19"/>
+      <c r="E181" s="19"/>
+    </row>
+    <row r="182" spans="4:5">
+      <c r="D182" s="19"/>
+      <c r="E182" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2207,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -2218,64 +4069,64 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>109</v>
+        <v>250</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>110</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>112</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>113</v>
+        <v>254</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>114</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>116</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>117</v>
+        <v>258</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>118</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>119</v>
+        <v>260</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>120</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>121</v>
+        <v>262</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>122</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2283,10 +4134,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>124</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2294,10 +4145,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>126</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2305,10 +4156,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>127</v>
+        <v>268</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>128</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2316,10 +4167,10 @@
         <v>5</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>129</v>
+        <v>270</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>130</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2328,7 +4179,7 @@
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="5" t="s">
-        <v>131</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2337,7 +4188,7 @@
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="5" t="s">
-        <v>131</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2345,19 +4196,19 @@
         <v>8</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>132</v>
+        <v>273</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>133</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>134</v>
+        <v>275</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>135</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2365,10 +4216,10 @@
         <v>9</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>137</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2377,7 +4228,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="5" t="s">
-        <v>131</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
